--- a/Employee_Reports_wi52/Meegle Mathew Q0483.xlsx
+++ b/Employee_Reports_wi52/Meegle Mathew Q0483.xlsx
@@ -539,20 +539,20 @@
       <c r="E3" s="3" t="inlineStr"/>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>05-Oct-2025</t>
+          <t>26-Aug-2026</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>05-Oct-2027</t>
+          <t>25-Aug-2028</t>
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>411</v>
+        <v>728</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
